--- a/src/main/resources/test_excel.xlsx
+++ b/src/main/resources/test_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学习\hot-news-backend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435CB976-3973-4FF4-8D63-705A424F5EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055F10BE-26DE-497E-B5A7-12BB0C1D0EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="3690" windowWidth="21600" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="1950" windowWidth="21600" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,31 +25,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>apiName</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>apiAddress</t>
+    <t>platform</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apiParam</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>apiDescribe</t>
-  </si>
-  <si>
-    <t>51CTO推荐榜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.toutiao.com/hot-event/hot-board/?origin=toutiao_pc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>今日头条热榜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://api-media.51cto.com/index/index/recommend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://i.news.qq.com/web_feed/getPCList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apiURL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯娱乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qqnews_ent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_ent",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯娱乐热点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -102,11 +127,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -389,54 +417,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="75.875" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="1" max="1" width="14.375" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="38.25" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{A6B0CDF8-BD50-404F-80B2-6AE3300F5268}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{DC2AB80E-7ACB-4D1D-B092-7E81183AA6B4}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{5B8D2A43-8E13-4470-8A36-A5D55B02C82C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/src/main/resources/test_excel.xlsx
+++ b/src/main/resources/test_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学习\hot-news-backend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{055F10BE-26DE-497E-B5A7-12BB0C1D0EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4842AFB6-7D63-48AB-8DC0-7CD914609C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="1950" windowWidth="21600" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="45">
   <si>
     <t>apiName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,30 +51,291 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>腾讯娱乐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qqnews_ent</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{
-  "base_req": {
-    "from": "pc"
-  },
-  "forward": "2",
-  "qimei36": "0_b8a8jkD5Gb6D3",
-  "device_id": "0_b8a8jkD5Gb6D3",
-  "flush_num": 1,
-  "channel_id": "news_news_ent",
-  "item_count": 12,
-  "is_local_chlid": "0"
-}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>腾讯娱乐热点</t>
+    <t>qq_news_sports</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯体育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯体育热点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_sports",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯财经</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_finance",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯财经热点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_tech</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯科技热点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_tech",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_nba</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯NBA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_nba",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_world</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯国际</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_world",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_war</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯军事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_mil",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_edu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯教育</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_edu",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_health</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯健康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_antip",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_games</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯游戏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_game",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_baby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯育儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_baby",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_esport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯电竞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_esport",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qq_news_kepu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>腾讯科学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+  "base_req": {
+    "from": "pc"
+  },
+  "forward": "2",
+  "qimei36": "0_b8a8jkD5Gb6D3",
+  "device_id": "0_b8a8jkD5Gb6D3",
+  "flush_num": 1,
+  "channel_id": "news_news_kepu",
+  "item_count": 12,
+  "is_local_chlid": "0"
+}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -127,15 +388,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -417,59 +679,248 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.375" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="38.25" customWidth="1"/>
-    <col min="4" max="4" width="19.875" customWidth="1"/>
-    <col min="5" max="5" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="14.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="38.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="28.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="213.75" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="C3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{5B8D2A43-8E13-4470-8A36-A5D55B02C82C}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{D700AE0B-5C52-4E94-867B-757FF3F6CB61}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{07E87A8F-C449-479E-B788-A95465ED1760}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{67115335-29BD-4DE5-8180-ECBE933D6292}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{652B1537-6647-4525-B858-7ABFCD0C5CF8}"/>
+    <hyperlink ref="C6:C13" r:id="rId5" display="https://i.news.qq.com/web_feed/getPCList" xr:uid="{FDDE1578-D28A-43D8-B190-D8AD5BFBC5BA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>